--- a/仕様書.xlsx
+++ b/仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y_nakahira\Documents\GitHub\2025Summer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FCC8C95-FBA3-4F2E-98F1-EB04D12160BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C961FAE8-D56B-434E-9D7E-C085F43B55CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3360" yWindow="900" windowWidth="21600" windowHeight="12645" firstSheet="10" activeTab="13" xr2:uid="{DF94D868-592B-4338-B7CA-B1CACE85BD54}"/>
+    <workbookView xWindow="-23805" yWindow="2565" windowWidth="21600" windowHeight="12645" firstSheet="10" activeTab="12" xr2:uid="{DF94D868-592B-4338-B7CA-B1CACE85BD54}"/>
   </bookViews>
   <sheets>
     <sheet name="全体概要" sheetId="4" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="396">
   <si>
     <t>ロゴ</t>
     <phoneticPr fontId="1"/>
@@ -3280,6 +3280,159 @@
   </si>
   <si>
     <t>Debugビルドのみ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャスト回避用の当たり判定を用意する</t>
+    <rPh sb="4" eb="6">
+      <t>カイヒ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ヨウイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーの技が生きるように敵を調整する</t>
+    <rPh sb="6" eb="7">
+      <t>ワザ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>チョウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームが始まれば自動的にチュートリアル</t>
+    <rPh sb="4" eb="5">
+      <t>ハジ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>ジドウテキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>←面白さ</t>
+    <rPh sb="1" eb="3">
+      <t>オモシロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チュートリアルは実際のゲーム中に操作を教えるだけ</t>
+    <rPh sb="8" eb="10">
+      <t>ジッサイ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>オシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>できる行動をボタンガイドで表示</t>
+    <rPh sb="3" eb="5">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>選択した技が刺さるような敵の配置(チュートリアル)</t>
+    <rPh sb="0" eb="2">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ワザ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>サ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ハイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8/20すること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>技（追加、強化）</t>
+    <rPh sb="0" eb="1">
+      <t>ワザ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>キョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>技に意味を持たせる</t>
+    <rPh sb="0" eb="1">
+      <t>ワザ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イミ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵のパラメータを操作できるようにする</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ソウサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>回避用当たり判定</t>
+    <rPh sb="0" eb="2">
+      <t>カイヒ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ハンテイ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3705,7 +3858,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3848,9 +4001,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -8401,7 +8551,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3A3D13C-AD92-4326-A839-9A5F8A35AE3A}">
-  <dimension ref="D3:AM32"/>
+  <dimension ref="A3:AM42"/>
   <sheetFormatPr defaultColWidth="3.25" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="3" spans="7:39" x14ac:dyDescent="0.4">
@@ -8517,6 +8667,89 @@
     <row r="32" spans="4:4" x14ac:dyDescent="0.4">
       <c r="D32" t="s">
         <v>374</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>74</v>
+      </c>
+      <c r="B36" t="s">
+        <v>384</v>
+      </c>
+      <c r="W36" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
+        <v>74</v>
+      </c>
+      <c r="B37" t="s">
+        <v>385</v>
+      </c>
+      <c r="N37" t="s">
+        <v>387</v>
+      </c>
+      <c r="W37" t="s">
+        <v>74</v>
+      </c>
+      <c r="X37" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
+        <v>74</v>
+      </c>
+      <c r="B38" t="s">
+        <v>386</v>
+      </c>
+      <c r="W38" t="s">
+        <v>74</v>
+      </c>
+      <c r="X38" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.4">
+      <c r="A39" t="s">
+        <v>74</v>
+      </c>
+      <c r="B39" t="s">
+        <v>388</v>
+      </c>
+      <c r="W39" t="s">
+        <v>74</v>
+      </c>
+      <c r="X39" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.4">
+      <c r="A40" t="s">
+        <v>74</v>
+      </c>
+      <c r="B40" t="s">
+        <v>389</v>
+      </c>
+      <c r="W40" t="s">
+        <v>74</v>
+      </c>
+      <c r="X40" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.4">
+      <c r="A41" t="s">
+        <v>74</v>
+      </c>
+      <c r="B41" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.4">
+      <c r="A42" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -8545,8 +8778,8 @@
         <v>375</v>
       </c>
     </row>
-    <row r="6" spans="2:2" s="48" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="48" t="s">
+    <row r="6" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B6" t="s">
         <v>368</v>
       </c>
     </row>
@@ -11166,6 +11399,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="26553de7-2a3a-444c-a024-df4cb947fd03" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101005F0D9E193D28814892BA96752E68B42F" ma:contentTypeVersion="12" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="215e7263a294d62634617b65be5e81fd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c" xmlns:ns3="26553de7-2a3a-444c-a024-df4cb947fd03" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6aa5db53fbf3e176f355664c77c2c9ef" ns2:_="" ns3:_="">
     <xsd:import namespace="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
@@ -11366,27 +11619,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5133F06B-0556-4887-9A4E-22EA032BC896}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
+    <ds:schemaRef ds:uri="26553de7-2a3a-444c-a024-df4cb947fd03"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="26553de7-2a3a-444c-a024-df4cb947fd03" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF99FEAD-80A2-47F3-ACCA-BE8E1C14FBEC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49EC609C-331C-4105-80CF-9D6A995C6BFB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11403,23 +11655,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF99FEAD-80A2-47F3-ACCA-BE8E1C14FBEC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5133F06B-0556-4887-9A4E-22EA032BC896}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
-    <ds:schemaRef ds:uri="26553de7-2a3a-444c-a024-df4cb947fd03"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/仕様書.xlsx
+++ b/仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y_nakahira\Documents\GitHub\2025Summer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C961FAE8-D56B-434E-9D7E-C085F43B55CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CCA2930-2BC9-40C6-82CB-C0609480DA79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23805" yWindow="2565" windowWidth="21600" windowHeight="12645" firstSheet="10" activeTab="12" xr2:uid="{DF94D868-592B-4338-B7CA-B1CACE85BD54}"/>
+    <workbookView xWindow="-25545" yWindow="3345" windowWidth="21600" windowHeight="12645" firstSheet="10" activeTab="12" xr2:uid="{DF94D868-592B-4338-B7CA-B1CACE85BD54}"/>
   </bookViews>
   <sheets>
     <sheet name="全体概要" sheetId="4" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="417">
   <si>
     <t>ロゴ</t>
     <phoneticPr fontId="1"/>
@@ -3432,6 +3432,173 @@
     </rPh>
     <rPh sb="6" eb="8">
       <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャンプの挙動を改善したい</t>
+    <rPh sb="5" eb="7">
+      <t>キョドウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カイゼン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>どのように</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>上昇速く</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウショウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ハヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>頂点で滞空</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>落下は自然に</t>
+    <rPh sb="0" eb="2">
+      <t>ラッカ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シゼン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8/21すること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵のリアクション</t>
+  </si>
+  <si>
+    <t>吹き飛ぶリアクション</t>
+    <rPh sb="0" eb="1">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>追撃するアクションを作る</t>
+    <rPh sb="0" eb="2">
+      <t>ツイゲキ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>瞬間移動？引き寄せ？</t>
+    <rPh sb="0" eb="4">
+      <t>シュンカンイドウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャンプの挙動を改善する</t>
+    <rPh sb="5" eb="7">
+      <t>キョドウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カイゼン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵がコンボを最後までくらってくれる</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>サイゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーの問題点</t>
+    <rPh sb="6" eb="9">
+      <t>モンダイテン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テンポ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DMCをもっと参考にする</t>
+    <rPh sb="7" eb="9">
+      <t>サンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃のヒットストップ、エフェクト、ノックバックの強さとタイミング</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ツヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームが始まったときに演出</t>
+    <rPh sb="4" eb="5">
+      <t>ハジ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>エンシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵出現時エフェクト</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="1" eb="4">
+      <t>シュツゲンジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ロックオンしていないとき、コンボがつながらない</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵の質を上げる</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>シツ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8551,7 +8718,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3A3D13C-AD92-4326-A839-9A5F8A35AE3A}">
-  <dimension ref="A3:AM42"/>
+  <dimension ref="A3:AM61"/>
   <sheetFormatPr defaultColWidth="3.25" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="3" spans="7:39" x14ac:dyDescent="0.4">
@@ -8669,7 +8836,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:29" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
         <v>74</v>
       </c>
@@ -8680,7 +8847,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:29" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
         <v>74</v>
       </c>
@@ -8697,7 +8864,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:29" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
         <v>74</v>
       </c>
@@ -8711,7 +8878,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:29" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
         <v>74</v>
       </c>
@@ -8725,7 +8892,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:29" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
         <v>74</v>
       </c>
@@ -8739,7 +8906,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:29" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
         <v>74</v>
       </c>
@@ -8747,9 +8914,135 @@
         <v>390</v>
       </c>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:29" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
         <v>74</v>
+      </c>
+      <c r="B42" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="43" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="A43" t="s">
+        <v>74</v>
+      </c>
+      <c r="B43" t="s">
+        <v>416</v>
+      </c>
+      <c r="W43" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="44" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="W44" t="s">
+        <v>74</v>
+      </c>
+      <c r="X44" t="s">
+        <v>402</v>
+      </c>
+      <c r="AC44" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="45" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="W45" t="s">
+        <v>74</v>
+      </c>
+      <c r="X45" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="46" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="C46" t="s">
+        <v>396</v>
+      </c>
+      <c r="X46" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="47" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="W47" t="s">
+        <v>74</v>
+      </c>
+      <c r="X47" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="48" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="C48" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="50" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C50" t="s">
+        <v>74</v>
+      </c>
+      <c r="D50" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="51" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C51" t="s">
+        <v>74</v>
+      </c>
+      <c r="D51" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="52" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C52" t="s">
+        <v>74</v>
+      </c>
+      <c r="D52" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="56" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C56" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="57" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C57" t="s">
+        <v>74</v>
+      </c>
+      <c r="D57" t="s">
+        <v>409</v>
+      </c>
+      <c r="G57" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="58" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="D58" t="s">
+        <v>411</v>
+      </c>
+      <c r="E58" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="59" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C59" t="s">
+        <v>74</v>
+      </c>
+      <c r="D59" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="60" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C60" t="s">
+        <v>74</v>
+      </c>
+      <c r="D60" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="61" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C61" t="s">
+        <v>74</v>
+      </c>
+      <c r="D61" t="s">
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -11399,26 +11692,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="26553de7-2a3a-444c-a024-df4cb947fd03" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101005F0D9E193D28814892BA96752E68B42F" ma:contentTypeVersion="12" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="215e7263a294d62634617b65be5e81fd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c" xmlns:ns3="26553de7-2a3a-444c-a024-df4cb947fd03" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6aa5db53fbf3e176f355664c77c2c9ef" ns2:_="" ns3:_="">
     <xsd:import namespace="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
@@ -11619,26 +11892,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5133F06B-0556-4887-9A4E-22EA032BC896}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
-    <ds:schemaRef ds:uri="26553de7-2a3a-444c-a024-df4cb947fd03"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF99FEAD-80A2-47F3-ACCA-BE8E1C14FBEC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="26553de7-2a3a-444c-a024-df4cb947fd03" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49EC609C-331C-4105-80CF-9D6A995C6BFB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11655,4 +11929,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF99FEAD-80A2-47F3-ACCA-BE8E1C14FBEC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5133F06B-0556-4887-9A4E-22EA032BC896}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
+    <ds:schemaRef ds:uri="26553de7-2a3a-444c-a024-df4cb947fd03"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/仕様書.xlsx
+++ b/仕様書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y_nakahira\Documents\GitHub\2025Summer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CCA2930-2BC9-40C6-82CB-C0609480DA79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FD1CAD3-E634-44EF-BDA9-7FCE162C95A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-25545" yWindow="3345" windowWidth="21600" windowHeight="12645" firstSheet="10" activeTab="12" xr2:uid="{DF94D868-592B-4338-B7CA-B1CACE85BD54}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="423">
   <si>
     <t>ロゴ</t>
     <phoneticPr fontId="1"/>
@@ -3599,6 +3599,87 @@
     </rPh>
     <rPh sb="4" eb="5">
       <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>具体的な処理</t>
+    <rPh sb="0" eb="3">
+      <t>グタイテキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ショリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャンプ開始時、上方向への抵抗を強める</t>
+    <rPh sb="4" eb="7">
+      <t>カイシジ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>ウエホウコウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>テイコウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ツヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>より強い力で上昇</t>
+    <rPh sb="2" eb="3">
+      <t>ツヨ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>チカラ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→素早く上昇して、素早く停止する</t>
+    <rPh sb="1" eb="3">
+      <t>スバヤ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジョウショウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>スバヤ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>テイシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→落下も遅くなる</t>
+    <rPh sb="1" eb="3">
+      <t>ラッカ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>オソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一定時間したら抵抗を元に戻す</t>
+    <rPh sb="0" eb="4">
+      <t>イッテイジカン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>テイコウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>モド</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8718,7 +8799,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3A3D13C-AD92-4326-A839-9A5F8A35AE3A}">
-  <dimension ref="A3:AM61"/>
+  <dimension ref="A3:AM65"/>
   <sheetFormatPr defaultColWidth="3.25" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="3" spans="7:39" x14ac:dyDescent="0.4">
@@ -8997,44 +9078,45 @@
         <v>400</v>
       </c>
     </row>
+    <row r="53" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C53" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="54" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C54" t="s">
+        <v>74</v>
+      </c>
+      <c r="D54" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="55" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="D55" t="s">
+        <v>419</v>
+      </c>
+    </row>
     <row r="56" spans="3:7" x14ac:dyDescent="0.4">
-      <c r="C56" t="s">
-        <v>408</v>
+      <c r="D56" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="57" spans="3:7" x14ac:dyDescent="0.4">
-      <c r="C57" t="s">
+      <c r="D57" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="58" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C58" t="s">
         <v>74</v>
       </c>
-      <c r="D57" t="s">
-        <v>409</v>
-      </c>
-      <c r="G57" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="58" spans="3:7" x14ac:dyDescent="0.4">
       <c r="D58" t="s">
-        <v>411</v>
-      </c>
-      <c r="E58" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="59" spans="3:7" x14ac:dyDescent="0.4">
-      <c r="C59" t="s">
-        <v>74</v>
-      </c>
-      <c r="D59" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
     </row>
     <row r="60" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C60" t="s">
-        <v>74</v>
-      </c>
-      <c r="D60" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
     </row>
     <row r="61" spans="3:7" x14ac:dyDescent="0.4">
@@ -9042,6 +9124,41 @@
         <v>74</v>
       </c>
       <c r="D61" t="s">
+        <v>409</v>
+      </c>
+      <c r="G61" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="62" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="D62" t="s">
+        <v>411</v>
+      </c>
+      <c r="E62" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="63" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C63" t="s">
+        <v>74</v>
+      </c>
+      <c r="D63" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="64" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C64" t="s">
+        <v>74</v>
+      </c>
+      <c r="D64" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="65" spans="3:4" x14ac:dyDescent="0.4">
+      <c r="C65" t="s">
+        <v>74</v>
+      </c>
+      <c r="D65" t="s">
         <v>415</v>
       </c>
     </row>
@@ -11692,6 +11809,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="26553de7-2a3a-444c-a024-df4cb947fd03" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101005F0D9E193D28814892BA96752E68B42F" ma:contentTypeVersion="12" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="215e7263a294d62634617b65be5e81fd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c" xmlns:ns3="26553de7-2a3a-444c-a024-df4cb947fd03" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6aa5db53fbf3e176f355664c77c2c9ef" ns2:_="" ns3:_="">
     <xsd:import namespace="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
@@ -11892,27 +12029,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5133F06B-0556-4887-9A4E-22EA032BC896}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
+    <ds:schemaRef ds:uri="26553de7-2a3a-444c-a024-df4cb947fd03"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="26553de7-2a3a-444c-a024-df4cb947fd03" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF99FEAD-80A2-47F3-ACCA-BE8E1C14FBEC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49EC609C-331C-4105-80CF-9D6A995C6BFB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11929,23 +12065,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF99FEAD-80A2-47F3-ACCA-BE8E1C14FBEC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5133F06B-0556-4887-9A4E-22EA032BC896}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
-    <ds:schemaRef ds:uri="26553de7-2a3a-444c-a024-df4cb947fd03"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/仕様書.xlsx
+++ b/仕様書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y_nakahira\Documents\GitHub\2025Summer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FD1CAD3-E634-44EF-BDA9-7FCE162C95A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F598756-D9AA-4754-8575-A430D0778D53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-25545" yWindow="3345" windowWidth="21600" windowHeight="12645" firstSheet="10" activeTab="12" xr2:uid="{DF94D868-592B-4338-B7CA-B1CACE85BD54}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="433">
   <si>
     <t>ロゴ</t>
     <phoneticPr fontId="1"/>
@@ -3680,6 +3680,112 @@
     </rPh>
     <rPh sb="12" eb="13">
       <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>IsGround、バグっている問題</t>
+    <rPh sb="15" eb="17">
+      <t>モンダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>問題点</t>
+    <rPh sb="0" eb="3">
+      <t>モンダイテン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャンプした瞬間、IsGruondにより着地する</t>
+    <rPh sb="6" eb="8">
+      <t>シュンカン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>チャクチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>浮き上がる瞬間、IsGroundにより着地する</t>
+    <rPh sb="0" eb="1">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シュンカン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>チャクチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>地面にいる状態で地面から離れる動作を行っても、一フレーム目ではIsGroundの条件を満たしてしまう</t>
+    <rPh sb="0" eb="2">
+      <t>ジメン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジメン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ドウサ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ジョウケン</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>解決方法</t>
+    <rPh sb="0" eb="4">
+      <t>カイケツホウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>IsGroundの設定タイミングを変える</t>
+    <rPh sb="9" eb="11">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>どこに</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャンプするときに、IsGroundをfalseにしてしまう</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3種</t>
+    <rPh sb="1" eb="2">
+      <t>シュ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8799,7 +8905,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3A3D13C-AD92-4326-A839-9A5F8A35AE3A}">
-  <dimension ref="A3:AM65"/>
+  <dimension ref="A3:AO80"/>
   <sheetFormatPr defaultColWidth="3.25" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="3" spans="7:39" x14ac:dyDescent="0.4">
@@ -9154,12 +9260,80 @@
         <v>414</v>
       </c>
     </row>
-    <row r="65" spans="3:4" x14ac:dyDescent="0.4">
+    <row r="65" spans="3:41" x14ac:dyDescent="0.4">
       <c r="C65" t="s">
         <v>74</v>
       </c>
       <c r="D65" t="s">
         <v>415</v>
+      </c>
+    </row>
+    <row r="70" spans="3:41" x14ac:dyDescent="0.4">
+      <c r="C70" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="71" spans="3:41" x14ac:dyDescent="0.4">
+      <c r="AO71" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="72" spans="3:41" x14ac:dyDescent="0.4">
+      <c r="C72" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="73" spans="3:41" x14ac:dyDescent="0.4">
+      <c r="C73" t="s">
+        <v>74</v>
+      </c>
+      <c r="D73" t="s">
+        <v>425</v>
+      </c>
+      <c r="P73" t="s">
+        <v>426</v>
+      </c>
+      <c r="AN73" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="74" spans="3:41" x14ac:dyDescent="0.4">
+      <c r="D74" t="s">
+        <v>411</v>
+      </c>
+      <c r="E74" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="75" spans="3:41" x14ac:dyDescent="0.4">
+      <c r="C75" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="77" spans="3:41" x14ac:dyDescent="0.4">
+      <c r="C77" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="78" spans="3:41" x14ac:dyDescent="0.4">
+      <c r="C78" t="s">
+        <v>74</v>
+      </c>
+      <c r="D78" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="79" spans="3:41" x14ac:dyDescent="0.4">
+      <c r="D79" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="80" spans="3:41" x14ac:dyDescent="0.4">
+      <c r="C80" t="s">
+        <v>74</v>
+      </c>
+      <c r="D80" t="s">
+        <v>431</v>
       </c>
     </row>
   </sheetData>

--- a/仕様書.xlsx
+++ b/仕様書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y_nakahira\Documents\GitHub\2025Summer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F598756-D9AA-4754-8575-A430D0778D53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{980CDD84-6ACA-4751-A57D-C5E7DFCEF0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-25545" yWindow="3345" windowWidth="21600" windowHeight="12645" firstSheet="10" activeTab="12" xr2:uid="{DF94D868-592B-4338-B7CA-B1CACE85BD54}"/>
   </bookViews>
@@ -11983,26 +11983,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="26553de7-2a3a-444c-a024-df4cb947fd03" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101005F0D9E193D28814892BA96752E68B42F" ma:contentTypeVersion="12" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="215e7263a294d62634617b65be5e81fd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c" xmlns:ns3="26553de7-2a3a-444c-a024-df4cb947fd03" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6aa5db53fbf3e176f355664c77c2c9ef" ns2:_="" ns3:_="">
     <xsd:import namespace="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
@@ -12203,26 +12183,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5133F06B-0556-4887-9A4E-22EA032BC896}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
-    <ds:schemaRef ds:uri="26553de7-2a3a-444c-a024-df4cb947fd03"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF99FEAD-80A2-47F3-ACCA-BE8E1C14FBEC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="26553de7-2a3a-444c-a024-df4cb947fd03" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49EC609C-331C-4105-80CF-9D6A995C6BFB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12239,4 +12220,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF99FEAD-80A2-47F3-ACCA-BE8E1C14FBEC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5133F06B-0556-4887-9A4E-22EA032BC896}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
+    <ds:schemaRef ds:uri="26553de7-2a3a-444c-a024-df4cb947fd03"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/仕様書.xlsx
+++ b/仕様書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y_nakahira\Documents\GitHub\2025Summer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{980CDD84-6ACA-4751-A57D-C5E7DFCEF0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C208B184-C295-41E2-BDD1-D3EE72BEAFF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-25545" yWindow="3345" windowWidth="21600" windowHeight="12645" firstSheet="10" activeTab="12" xr2:uid="{DF94D868-592B-4338-B7CA-B1CACE85BD54}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="451">
   <si>
     <t>ロゴ</t>
     <phoneticPr fontId="1"/>
@@ -3786,6 +3786,234 @@
     <t>3種</t>
     <rPh sb="1" eb="2">
       <t>シュ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>インターン振り返り</t>
+    <rPh sb="5" eb="6">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>カエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>何を制作したか</t>
+    <rPh sb="0" eb="1">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>セイサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今回の全体を通しての成果</t>
+    <rPh sb="0" eb="2">
+      <t>コンカイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>トオ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>セイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>明日からどうするか</t>
+    <rPh sb="0" eb="2">
+      <t>アシタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面共有して説明</t>
+    <rPh sb="0" eb="4">
+      <t>ガメンキョウユウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今回の成果</t>
+    <rPh sb="0" eb="2">
+      <t>コンカイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>セイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>照井さんと話していて、先に外部ファイルからの編集を容易にする設計や、思い描いたとおりの動きを指定しやすいシステム作りは大事だと思った。</t>
+    <rPh sb="0" eb="2">
+      <t>テルイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ガイブ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ヨウイ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>エガ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>ヅク</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>ダイジ</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>オモ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>やったこと</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UIエディター</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>打ち上げ技と空中技</t>
+    <rPh sb="0" eb="1">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ワザ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>クウチュウワザ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>瞬間移動</t>
+    <rPh sb="0" eb="4">
+      <t>シュンカンイドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>数多の調整とバグ修正</t>
+    <rPh sb="0" eb="2">
+      <t>アマタ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>チョウセイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャンプの挙動</t>
+    <rPh sb="5" eb="7">
+      <t>キョドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今の調子を落とさず毎日プロジェクトを触る</t>
+    <rPh sb="0" eb="1">
+      <t>イマ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>チョウシ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>マイニチ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>サワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一度実装してみる→一度Excelに起こしてみる</t>
+    <rPh sb="0" eb="2">
+      <t>イチド</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イチド</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敬遠してきた外部ファイル関連に慣れることができた</t>
+    <rPh sb="0" eb="2">
+      <t>ケイエン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ガイブ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カンレン</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ほかの人のソースコードを読む</t>
+    <rPh sb="3" eb="4">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>さらにプレイヤーの手触りをよくする</t>
+    <rPh sb="9" eb="11">
+      <t>テザワ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8905,7 +9133,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3A3D13C-AD92-4326-A839-9A5F8A35AE3A}">
-  <dimension ref="A3:AO80"/>
+  <dimension ref="A3:AO111"/>
   <sheetFormatPr defaultColWidth="3.25" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="3" spans="7:39" x14ac:dyDescent="0.4">
@@ -9334,6 +9562,104 @@
       </c>
       <c r="D80" t="s">
         <v>431</v>
+      </c>
+    </row>
+    <row r="85" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C85" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="87" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C87" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="88" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C88" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="89" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C89" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="91" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C91" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="93" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C93" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="95" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C95" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="96" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C96" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="97" spans="3:9" x14ac:dyDescent="0.4">
+      <c r="C97" t="s">
+        <v>442</v>
+      </c>
+      <c r="I97" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="98" spans="3:9" x14ac:dyDescent="0.4">
+      <c r="C98" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="99" spans="3:9" x14ac:dyDescent="0.4">
+      <c r="C99" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="102" spans="3:9" x14ac:dyDescent="0.4">
+      <c r="C102" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="103" spans="3:9" x14ac:dyDescent="0.4">
+      <c r="C103" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="104" spans="3:9" x14ac:dyDescent="0.4">
+      <c r="C104" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="107" spans="3:9" x14ac:dyDescent="0.4">
+      <c r="C107" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="108" spans="3:9" x14ac:dyDescent="0.4">
+      <c r="C108" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="109" spans="3:9" x14ac:dyDescent="0.4">
+      <c r="C109" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="110" spans="3:9" x14ac:dyDescent="0.4">
+      <c r="C110" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="111" spans="3:9" x14ac:dyDescent="0.4">
+      <c r="C111" t="s">
+        <v>450</v>
       </c>
     </row>
   </sheetData>

--- a/仕様書.xlsx
+++ b/仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y_nakahira\Documents\GitHub\2025Summer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C208B184-C295-41E2-BDD1-D3EE72BEAFF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C77CF83E-5E34-4D82-A9C0-C76D39F57FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25545" yWindow="3345" windowWidth="21600" windowHeight="12645" firstSheet="10" activeTab="12" xr2:uid="{DF94D868-592B-4338-B7CA-B1CACE85BD54}"/>
+    <workbookView xWindow="-25545" yWindow="3345" windowWidth="21600" windowHeight="12645" firstSheet="8" activeTab="12" xr2:uid="{DF94D868-592B-4338-B7CA-B1CACE85BD54}"/>
   </bookViews>
   <sheets>
     <sheet name="全体概要" sheetId="4" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="470">
   <si>
     <t>ロゴ</t>
     <phoneticPr fontId="1"/>
@@ -4014,6 +4014,211 @@
     <t>さらにプレイヤーの手触りをよくする</t>
     <rPh sb="9" eb="11">
       <t>テザワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲーム自体の完成も考える</t>
+    <rPh sb="3" eb="5">
+      <t>ジタイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カンガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Enemyの共通する状態を統一すべきかどうか</t>
+    <rPh sb="6" eb="8">
+      <t>キョウツウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>トウイツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>まずできるのか</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→できそう</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アニメーションの名前を統一すれば実現可能</t>
+    <rPh sb="8" eb="10">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>トウイツ</t>
+    </rPh>
+    <rPh sb="16" eb="20">
+      <t>ジツゲンカノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>統一して実装したい状態</t>
+    <rPh sb="0" eb="2">
+      <t>トウイツ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Stun状態</t>
+    <rPh sb="4" eb="6">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Death状態</t>
+    <rPh sb="5" eb="7">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>死亡</t>
+    <rPh sb="0" eb="2">
+      <t>シボウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>KnockUp状態</t>
+    <rPh sb="7" eb="9">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>その時に打ち上げ攻撃をくらうとKnockUp</t>
+    <rPh sb="2" eb="3">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スタン値が0になったらStun状態に移行　一定フレーム継続</t>
+    <rPh sb="3" eb="4">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>イコウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>イッテイ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ケイゾク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>その時に攻撃をくらうとダメージアニメーションを再生する</t>
+    <rPh sb="2" eb="3">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>サイセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Stunしていないときも攻撃を受けるとアクションしてほしいので、モデルを振動させる</t>
+    <rPh sb="12" eb="14">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>シンドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Stun時はより大きく振動する</t>
+    <rPh sb="4" eb="5">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>シンドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>起き上がり状態</t>
+    <rPh sb="0" eb="1">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>StunやKnockUpから回復するときのアニメーション。殴られてもびくともしない(スタン値の蓄積はする)</t>
+    <rPh sb="14" eb="16">
+      <t>カイフク</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ナグ</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>チクセキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>行動ができない。攻撃をくらうとダメージアニメーションを再生する</t>
+    <rPh sb="0" eb="2">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>サイセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>KnockUpアニメーションを再生する。それ以外の行動ができない。</t>
+    <rPh sb="15" eb="17">
+      <t>サイセイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -9133,7 +9338,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3A3D13C-AD92-4326-A839-9A5F8A35AE3A}">
-  <dimension ref="A3:AO111"/>
+  <dimension ref="A3:AO137"/>
   <sheetFormatPr defaultColWidth="3.25" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="3" spans="7:39" x14ac:dyDescent="0.4">
@@ -9660,6 +9865,93 @@
     <row r="111" spans="3:9" x14ac:dyDescent="0.4">
       <c r="C111" t="s">
         <v>450</v>
+      </c>
+    </row>
+    <row r="112" spans="3:9" x14ac:dyDescent="0.4">
+      <c r="C112" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="118" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C118" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="120" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C120" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="121" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C121" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="122" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C122" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="124" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C124" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="126" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C126" t="s">
+        <v>457</v>
+      </c>
+      <c r="G126" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="127" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C127" t="s">
+        <v>458</v>
+      </c>
+      <c r="G127" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="128" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C128" t="s">
+        <v>460</v>
+      </c>
+      <c r="G128" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="130" spans="3:8" x14ac:dyDescent="0.4">
+      <c r="C130" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="131" spans="3:8" x14ac:dyDescent="0.4">
+      <c r="C131" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="132" spans="3:8" x14ac:dyDescent="0.4">
+      <c r="C132" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="134" spans="3:8" x14ac:dyDescent="0.4">
+      <c r="C134" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="135" spans="3:8" x14ac:dyDescent="0.4">
+      <c r="C135" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="137" spans="3:8" x14ac:dyDescent="0.4">
+      <c r="C137" t="s">
+        <v>466</v>
+      </c>
+      <c r="H137" t="s">
+        <v>467</v>
       </c>
     </row>
   </sheetData>

--- a/仕様書.xlsx
+++ b/仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y_nakahira\Documents\GitHub\2025Summer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C77CF83E-5E34-4D82-A9C0-C76D39F57FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6E1C3F8-A48A-43A8-AB8E-A9FF382295ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25545" yWindow="3345" windowWidth="21600" windowHeight="12645" firstSheet="8" activeTab="12" xr2:uid="{DF94D868-592B-4338-B7CA-B1CACE85BD54}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="8" activeTab="12" xr2:uid="{DF94D868-592B-4338-B7CA-B1CACE85BD54}"/>
   </bookViews>
   <sheets>
     <sheet name="全体概要" sheetId="4" r:id="rId1"/>
@@ -9789,8 +9789,8 @@
         <v>436</v>
       </c>
     </row>
-    <row r="91" spans="3:3" x14ac:dyDescent="0.4">
-      <c r="C91" t="s">
+    <row r="91" spans="3:3" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="C91" s="1" t="s">
         <v>434</v>
       </c>
     </row>
@@ -9827,8 +9827,8 @@
         <v>444</v>
       </c>
     </row>
-    <row r="102" spans="3:9" x14ac:dyDescent="0.4">
-      <c r="C102" t="s">
+    <row r="102" spans="3:9" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="C102" s="1" t="s">
         <v>438</v>
       </c>
     </row>
@@ -9842,8 +9842,8 @@
         <v>448</v>
       </c>
     </row>
-    <row r="107" spans="3:9" x14ac:dyDescent="0.4">
-      <c r="C107" t="s">
+    <row r="107" spans="3:9" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="C107" s="1" t="s">
         <v>436</v>
       </c>
     </row>
@@ -12601,6 +12601,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="26553de7-2a3a-444c-a024-df4cb947fd03" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101005F0D9E193D28814892BA96752E68B42F" ma:contentTypeVersion="12" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="215e7263a294d62634617b65be5e81fd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c" xmlns:ns3="26553de7-2a3a-444c-a024-df4cb947fd03" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6aa5db53fbf3e176f355664c77c2c9ef" ns2:_="" ns3:_="">
     <xsd:import namespace="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
@@ -12801,27 +12821,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5133F06B-0556-4887-9A4E-22EA032BC896}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
+    <ds:schemaRef ds:uri="26553de7-2a3a-444c-a024-df4cb947fd03"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="26553de7-2a3a-444c-a024-df4cb947fd03" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF99FEAD-80A2-47F3-ACCA-BE8E1C14FBEC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49EC609C-331C-4105-80CF-9D6A995C6BFB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12838,23 +12857,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF99FEAD-80A2-47F3-ACCA-BE8E1C14FBEC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5133F06B-0556-4887-9A4E-22EA032BC896}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
-    <ds:schemaRef ds:uri="26553de7-2a3a-444c-a024-df4cb947fd03"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>